--- a/outputs/reports/stacked_ensemble_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/stacked_ensemble_v1/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1781127861529395</v>
+        <v>0.2219334719336754</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008332288532263421</v>
+        <v>0.001337719298245499</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=17.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=22.19%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.09715242881070832</v>
+        <v>0.09719334719342648</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004544884653962522</v>
+        <v>0.0005858395989973841</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=9.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.09659408151866568</v>
+        <v>0.09095634095640713</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004518764627214344</v>
+        <v>0.0005482456140349368</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.66%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.08096035734221936</v>
+        <v>0.06808731808737914</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003787403878300344</v>
+        <v>0.0004104010025062221</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=6.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.07146845337799287</v>
+        <v>0.06288981288986148</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0003343363423604639</v>
+        <v>0.0003790726817041734</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.29%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04578447794526556</v>
+        <v>0.05457380457383875</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002141842193246202</v>
+        <v>0.0003289473684209288</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.46%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.03852596314907911</v>
+        <v>0.04625779625782522</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001802281845537101</v>
+        <v>0.0002788220551377396</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=3.85%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.63%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03740926856505316</v>
+        <v>0.03638253638256838</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001750041792043522</v>
+        <v>0.000219298245614008</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=3.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03629257398101535</v>
+        <v>0.02754677754680401</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0001697801738549387</v>
+        <v>0.0001660401002506195</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.63%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0351758793969894</v>
+        <v>0.02390852390854809</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0001645561685055807</v>
+        <v>0.0001441102756892243</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.52%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.39%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/stacked_ensemble_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/stacked_ensemble_v1/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2219334719336754</v>
+        <v>0.1027335695024538</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001337719298245499</v>
+        <v>0.006969778495202472</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=22.19%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.09719334719342648</v>
+        <v>0.09652091154231966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005858395989973841</v>
+        <v>0.006548291633037551</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.09095634095640713</v>
+        <v>0.07809443240098939</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005482456140349368</v>
+        <v>0.005298179535467795</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.06808731808737914</v>
+        <v>0.06968751652302239</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0004104010025062221</v>
+        <v>0.00472782710070857</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=6.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.06288981288986148</v>
+        <v>0.05950933220535835</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0003790726817041734</v>
+        <v>0.004037306071204505</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.29%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05457380457383875</v>
+        <v>0.05448633215248471</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003289473684209288</v>
+        <v>0.003696529459241427</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.46%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04625779625782522</v>
+        <v>0.04909321630624239</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0002788220551377396</v>
+        <v>0.003330642991660082</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.63%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03638253638256838</v>
+        <v>0.04446676888912223</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000219298245614008</v>
+        <v>0.003016769796430951</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.02754677754680401</v>
+        <v>0.03666790038597665</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0001660401002506195</v>
+        <v>0.002487669267330406</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>보조금전용신용카드집행건수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02390852390854809</v>
+        <v>0.0365357161740591</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0001441102756892243</v>
+        <v>0.002478701461752442</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.39%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/stacked_ensemble_v1/feature_importance_top10.xlsx
+++ b/outputs/reports/stacked_ensemble_v1/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1027335695024538</v>
+        <v>0.2335976928622889</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006969778495202472</v>
+        <v>0.05302921809376565</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.36%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.09652091154231966</v>
+        <v>0.2134295499021494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006548291633037551</v>
+        <v>0.0484508301890102</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=21.34%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.07809443240098939</v>
+        <v>0.1053661551138105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005298179535467795</v>
+        <v>0.02391926371689701</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=10.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.06968751652302239</v>
+        <v>0.08503064167267367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00472782710070857</v>
+        <v>0.01930288089177007</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05950933220535835</v>
+        <v>0.04363863425687455</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004037306071204505</v>
+        <v>0.009906444815300897</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=4.36%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05448633215248471</v>
+        <v>0.03056442476053147</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003696529459241427</v>
+        <v>0.006938456997056974</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.06%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04909321630624239</v>
+        <v>0.02850448037902963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003330642991660082</v>
+        <v>0.006470827207870289</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=2.85%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04446676888912223</v>
+        <v>0.02491888968997853</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003016769796430951</v>
+        <v>0.005656859106067336</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=2.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03666790038597665</v>
+        <v>0.02480945514471095</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002487669267330406</v>
+        <v>0.005632016273516727</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=2.48%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>보조금전용신용카드집행건수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0365357161740591</v>
+        <v>0.02475151920898096</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002478701461752442</v>
+        <v>0.005618864185695793</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=2.48%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
